--- a/exports/CAMS_full_report.xlsx
+++ b/exports/CAMS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:U85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.93</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>568.8</v>
+        <v>558</v>
       </c>
       <c r="I2" t="n">
         <v>564.9840964816486</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>1.72</v>
+        <v>-0.21</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3</v>
+        <v>0.88</v>
       </c>
       <c r="M2" t="n">
         <v>0.64</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>4.36</v>
       </c>
       <c r="O2" t="n">
         <v>-0.21</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.62</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.38541666666</v>
+        <v>44593.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>546.1</v>
+        <v>552</v>
       </c>
       <c r="I3" t="n">
         <v>550.6408641355939</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>2.13</v>
+        <v>1.08</v>
       </c>
       <c r="L3" t="n">
         <v>1.76</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>6.79</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44600.38541666666</v>
+        <v>44600.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>546.7</v>
+        <v>538.4</v>
       </c>
       <c r="I4" t="n">
         <v>542.833526038415</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.96</v>
+        <v>-2.46</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2</v>
+        <v>2.79</v>
       </c>
       <c r="M4" t="n">
         <v>0.62</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.81</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44620.38541666666</v>
+        <v>44620.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>485.4</v>
+        <v>497</v>
       </c>
       <c r="I5" t="n">
         <v>495.6965648430245</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>9.84</v>
+        <v>7.69</v>
       </c>
       <c r="L5" t="n">
         <v>1.73</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>9.57</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44648.55208333334</v>
+        <v>44649.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>467.4</v>
+        <v>462.4</v>
       </c>
       <c r="I6" t="n">
         <v>464.8045222010002</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.96</v>
+        <v>-6.96</v>
       </c>
       <c r="L6" t="n">
-        <v>6.28</v>
+        <v>6.98</v>
       </c>
       <c r="M6" t="n">
         <v>3.32</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>6.06</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>462.4</v>
+        <v>485.4</v>
       </c>
       <c r="I7" t="n">
         <v>484.9704573195917</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-4.97</v>
       </c>
       <c r="L7" t="n">
-        <v>2.55</v>
+        <v>5.36</v>
       </c>
       <c r="M7" t="n">
         <v>0.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.28</v>
+        <v>4.48</v>
       </c>
       <c r="O7" t="n">
         <v>-1.18</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44683.38541666666</v>
+        <v>44683.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>494.1</v>
+        <v>487.8</v>
       </c>
       <c r="I8" t="n">
         <v>489.2253161581283</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>1.79</v>
+        <v>0.49</v>
       </c>
       <c r="L8" t="n">
         <v>4.37</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>6.5</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44711.55208333334</v>
+        <v>44712.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>425.4</v>
+        <v>450.4</v>
       </c>
       <c r="I9" t="n">
         <v>445.8799777099291</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>12.79</v>
+        <v>7.67</v>
       </c>
       <c r="L9" t="n">
         <v>1.85</v>
@@ -954,7 +1061,7 @@
         <v>1.74</v>
       </c>
       <c r="N9" t="n">
-        <v>4.58</v>
+        <v>9.26</v>
       </c>
       <c r="O9" t="n">
         <v>-1.05</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.42</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44726.38541666666</v>
+        <v>44726.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>478.6</v>
+        <v>467.8</v>
       </c>
       <c r="I10" t="n">
         <v>474.9671825576522</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>6.26</v>
+        <v>3.86</v>
       </c>
       <c r="L10" t="n">
         <v>5.42</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.37</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44753.55208333334</v>
+        <v>44754.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>454.8</v>
+        <v>462.8</v>
       </c>
       <c r="I11" t="n">
         <v>460.8202551795508</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>2.78</v>
+        <v>1.07</v>
       </c>
       <c r="L11" t="n">
         <v>7.31</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.18</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44778.38541666666</v>
+        <v>44778.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>488.8</v>
+        <v>472</v>
       </c>
       <c r="I12" t="n">
         <v>474.8891930451553</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>5.62</v>
+        <v>1.99</v>
       </c>
       <c r="L12" t="n">
         <v>2.25</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.91</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44811.55208333334</v>
+        <v>44812.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>461.2</v>
+        <v>472.4</v>
       </c>
       <c r="I13" t="n">
         <v>466.7883166308357</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K13" t="n">
-        <v>2.29</v>
+        <v>-0.08</v>
       </c>
       <c r="L13" t="n">
         <v>3.73</v>
@@ -1182,7 +1337,7 @@
         <v>2.21</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>3.17</v>
       </c>
       <c r="O13" t="n">
         <v>-3.67</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.72</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44823.38541666666</v>
+        <v>44823.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>496.8</v>
+        <v>494.2</v>
       </c>
       <c r="I14" t="n">
         <v>496.3127388823232</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>5.17</v>
+        <v>4.61</v>
       </c>
       <c r="L14" t="n">
         <v>1.78</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>5.47</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44845.55208333334</v>
+        <v>44846.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>511.2</v>
+        <v>515.9</v>
       </c>
       <c r="I15" t="n">
         <v>515.7965330898234</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.44</v>
+        <v>-4.39</v>
       </c>
       <c r="L15" t="n">
-        <v>4.98</v>
+        <v>5.16</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6.49</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44865.55208333334</v>
+        <v>44866.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>509.8</v>
+        <v>502.9</v>
       </c>
       <c r="I16" t="n">
         <v>504.1512827729923</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.18</v>
+        <v>-2.52</v>
       </c>
       <c r="L16" t="n">
-        <v>2.19</v>
+        <v>2.66</v>
       </c>
       <c r="M16" t="n">
         <v>0.36</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.73</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44893.38541666666</v>
+        <v>44893.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>469.8</v>
+        <v>473</v>
       </c>
       <c r="I17" t="n">
         <v>471.0280772682218</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>6.58</v>
+        <v>5.95</v>
       </c>
       <c r="L17" t="n">
         <v>1.69</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>4.28</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44896.38541666666</v>
+        <v>44896.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>456.6</v>
+        <v>454.9</v>
       </c>
       <c r="I18" t="n">
         <v>455.604013119649</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.47</v>
+        <v>-3.83</v>
       </c>
       <c r="L18" t="n">
-        <v>3.64</v>
+        <v>3.97</v>
       </c>
       <c r="M18" t="n">
         <v>-0</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>4.3</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>440.4</v>
+        <v>449.5</v>
       </c>
       <c r="I19" t="n">
         <v>449.3251611872932</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>3.19</v>
+        <v>1.19</v>
       </c>
       <c r="L19" t="n">
         <v>2.15</v>
@@ -1524,7 +1751,7 @@
         <v>0.82</v>
       </c>
       <c r="N19" t="n">
-        <v>1.42</v>
+        <v>2.27</v>
       </c>
       <c r="O19" t="n">
         <v>-1.17</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.22</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44953.55208333334</v>
+        <v>44956.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>457.8</v>
+        <v>453.6</v>
       </c>
       <c r="I20" t="n">
         <v>454.4515815736739</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K20" t="n">
-        <v>1.85</v>
+        <v>0.91</v>
       </c>
       <c r="L20" t="n">
         <v>4.34</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>4.09</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>451.6</v>
+        <v>466.2</v>
       </c>
       <c r="I21" t="n">
         <v>462.3097976889745</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K21" t="n">
-        <v>0.44</v>
+        <v>-2.78</v>
       </c>
       <c r="L21" t="n">
-        <v>2.78</v>
+        <v>3.57</v>
       </c>
       <c r="M21" t="n">
         <v>1.42</v>
       </c>
       <c r="N21" t="n">
-        <v>1.27</v>
+        <v>2.21</v>
       </c>
       <c r="O21" t="n">
         <v>-1.35</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>4.51</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>457.6</v>
+        <v>449.3</v>
       </c>
       <c r="I22" t="n">
         <v>449.8950574847377</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.84</v>
+        <v>-3.63</v>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>3.82</v>
       </c>
       <c r="M22" t="n">
         <v>0.82</v>
       </c>
       <c r="N22" t="n">
-        <v>0.74</v>
+        <v>1.92</v>
       </c>
       <c r="O22" t="n">
         <v>2.21</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>4.47</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>420.4</v>
+        <v>427.4</v>
       </c>
       <c r="I23" t="n">
         <v>421.585799693074</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>6.43</v>
+        <v>4.87</v>
       </c>
       <c r="L23" t="n">
         <v>2.03</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.83</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45029.55208333334</v>
+        <v>45033.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>426.4</v>
+        <v>420.4</v>
       </c>
       <c r="I24" t="n">
         <v>421.9367994825878</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>10</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.23</v>
+        <v>-1.64</v>
       </c>
       <c r="L24" t="n">
         <v>2.67</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>6.31</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45065.55208333334</v>
+        <v>45068.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>417</v>
+        <v>428.1</v>
       </c>
       <c r="I25" t="n">
         <v>424.3239744929355</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8100000000000001</v>
+        <v>-1.83</v>
       </c>
       <c r="L25" t="n">
-        <v>2.14</v>
+        <v>2.76</v>
       </c>
       <c r="M25" t="n">
         <v>0.68</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.14</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45103.55208333334</v>
+        <v>45104.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>429.3</v>
+        <v>428</v>
       </c>
       <c r="I26" t="n">
         <v>429.1896257205487</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K26" t="n">
-        <v>0.28</v>
+        <v>-0.02</v>
       </c>
       <c r="L26" t="n">
         <v>2.66</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>3.91</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45107.55208333334</v>
+        <v>45110.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>439.4</v>
+        <v>459.4</v>
       </c>
       <c r="I27" t="n">
         <v>441.3776939749284</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.66</v>
+        <v>-7.34</v>
       </c>
       <c r="L27" t="n">
-        <v>3.97</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>4.46</v>
       </c>
       <c r="O27" t="n">
         <v>-0.47</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>5.77</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45162.55208333334</v>
+        <v>45163.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="I28" t="n">
         <v>483.9917332945079</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K28" t="n">
-        <v>6.23</v>
+        <v>5.14</v>
       </c>
       <c r="L28" t="n">
         <v>3.35</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>5.91</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45174.55208333334</v>
+        <v>45175.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>488</v>
+        <v>493.7</v>
       </c>
       <c r="I29" t="n">
         <v>491.3166271783494</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.04</v>
+        <v>-2.22</v>
       </c>
       <c r="L29" t="n">
-        <v>2.77</v>
+        <v>3.69</v>
       </c>
       <c r="M29" t="n">
         <v>0.38</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>4.66</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45205.55208333334</v>
+        <v>45208.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>499</v>
+        <v>483.3</v>
       </c>
       <c r="I30" t="n">
         <v>489.5444848003316</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K30" t="n">
-        <v>1.07</v>
+        <v>-2.11</v>
       </c>
       <c r="L30" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
-        <v>0.44</v>
+        <v>1.76</v>
       </c>
       <c r="N30" t="n">
-        <v>2.35</v>
+        <v>3.53</v>
       </c>
       <c r="O30" t="n">
         <v>1.39</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>6.18</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45210.55208333334</v>
+        <v>45211.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>482.7</v>
+        <v>513.7</v>
       </c>
       <c r="I31" t="n">
         <v>505.3729135217463</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.12</v>
+        <v>-6.29</v>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>6.97</v>
       </c>
       <c r="M31" t="n">
         <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>0.46</v>
+        <v>5.95</v>
       </c>
       <c r="O31" t="n">
         <v>-3.53</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.23</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>499.4</v>
+        <v>486.2</v>
       </c>
       <c r="I32" t="n">
         <v>493.5853002883503</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.78</v>
+        <v>-5.35</v>
       </c>
       <c r="L32" t="n">
         <v>5.53</v>
@@ -2265,7 +2648,7 @@
         <v>0.33</v>
       </c>
       <c r="N32" t="n">
-        <v>2.52</v>
+        <v>3.48</v>
       </c>
       <c r="O32" t="n">
         <v>5.95</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.72</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45233.38541666666</v>
+        <v>45233.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>467.4</v>
+        <v>478.6</v>
       </c>
       <c r="I33" t="n">
         <v>471.9867770768213</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>3.87</v>
+        <v>1.56</v>
       </c>
       <c r="L33" t="n">
         <v>3.54</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.76</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45268.55208333334</v>
+        <v>45271.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>549</v>
+        <v>540.8</v>
       </c>
       <c r="I34" t="n">
         <v>547.2302113863124</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>35</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K34" t="n">
-        <v>14.71</v>
+        <v>13</v>
       </c>
       <c r="L34" t="n">
         <v>2.38</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.62</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45295.55208333334</v>
+        <v>45296.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>541.8</v>
+        <v>552.5</v>
       </c>
       <c r="I35" t="n">
         <v>550.5135497654105</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.18</v>
+        <v>-2.16</v>
       </c>
       <c r="L35" t="n">
         <v>2.57</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>4.9</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45314.38541666666</v>
+        <v>45314.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>552</v>
+        <v>549.8</v>
       </c>
       <c r="I36" t="n">
         <v>551.9464530859772</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.09</v>
+        <v>-0.49</v>
       </c>
       <c r="L36" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="M36" t="n">
         <v>1.09</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>4.39</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45321.55208333334</v>
+        <v>45322.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>553.6</v>
+        <v>580.8</v>
       </c>
       <c r="I37" t="n">
         <v>569.7388480962484</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-5.64</v>
       </c>
       <c r="L37" t="n">
-        <v>3.13</v>
+        <v>6.77</v>
       </c>
       <c r="M37" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="N37" t="n">
-        <v>0.84</v>
+        <v>4.37</v>
       </c>
       <c r="O37" t="n">
         <v>-0.51</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.94</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45357.55208333334</v>
+        <v>45358.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>592.4</v>
+        <v>584.8</v>
       </c>
       <c r="I38" t="n">
         <v>587.147107505732</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L38" t="n">
         <v>4.39</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>9.24</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45372.55208333334</v>
+        <v>45373.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>586.2</v>
+        <v>623.3</v>
       </c>
       <c r="I39" t="n">
         <v>611.9217296609238</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.24</v>
+        <v>-6.58</v>
       </c>
       <c r="L39" t="n">
-        <v>4.27</v>
+        <v>7.27</v>
       </c>
       <c r="M39" t="n">
         <v>1.13</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>12.24</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45421.38541666666</v>
+        <v>45421.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>638.2</v>
+        <v>621.4</v>
       </c>
       <c r="I40" t="n">
         <v>628.2460407505667</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K40" t="n">
-        <v>2.39</v>
+        <v>-0.3</v>
       </c>
       <c r="L40" t="n">
         <v>7.08</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45433.55208333334</v>
+        <v>45434.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>678</v>
+        <v>698.8</v>
       </c>
       <c r="I41" t="n">
         <v>678.6115024017303</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>-9.109999999999999</v>
+        <v>-12.46</v>
       </c>
       <c r="L41" t="n">
-        <v>9.75</v>
+        <v>13.78</v>
       </c>
       <c r="M41" t="n">
         <v>1.28</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.42</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>708.1</v>
+        <v>649.5</v>
       </c>
       <c r="I42" t="n">
         <v>664.1430499090031</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K42" t="n">
-        <v>1.33</v>
+        <v>-7.05</v>
       </c>
       <c r="L42" t="n">
-        <v>4.41</v>
+        <v>12.71</v>
       </c>
       <c r="M42" t="n">
         <v>0.58</v>
       </c>
       <c r="N42" t="n">
-        <v>3.61</v>
+        <v>6.79</v>
       </c>
       <c r="O42" t="n">
         <v>2.92</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>13.59</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45467.55208333334</v>
+        <v>45468.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>732</v>
+        <v>742.8</v>
       </c>
       <c r="I43" t="n">
         <v>734.2464666163368</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>-12.7</v>
+        <v>-14.36</v>
       </c>
       <c r="L43" t="n">
-        <v>13.5</v>
+        <v>18.18</v>
       </c>
       <c r="M43" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="N43" t="n">
         <v>5.02</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.73</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>874</v>
+        <v>811.5</v>
       </c>
       <c r="I44" t="n">
         <v>859.040416464334</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K44" t="n">
-        <v>17.66</v>
+        <v>9.25</v>
       </c>
       <c r="L44" t="n">
         <v>4.98</v>
       </c>
       <c r="M44" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="N44" t="n">
-        <v>3.13</v>
+        <v>9.68</v>
       </c>
       <c r="O44" t="n">
         <v>0.82</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>14.6</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45512.55208333334</v>
+        <v>45513.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>857</v>
+        <v>873</v>
       </c>
       <c r="I45" t="n">
         <v>871.6735271947741</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.61</v>
+        <v>-7.58</v>
       </c>
       <c r="L45" t="n">
-        <v>7.85</v>
+        <v>9.43</v>
       </c>
       <c r="M45" t="n">
         <v>3.75</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.83</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45569.38541666666</v>
+        <v>45569.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>862.5</v>
+        <v>853.2</v>
       </c>
       <c r="I46" t="n">
         <v>862.4090340092273</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.2</v>
+        <v>-2.27</v>
       </c>
       <c r="L46" t="n">
         <v>6.53</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>7.72</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45574.55208333334</v>
+        <v>45575.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>882.8</v>
+        <v>896.8</v>
       </c>
       <c r="I47" t="n">
         <v>892.0534821447139</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.47</v>
+        <v>-5.11</v>
       </c>
       <c r="L47" t="n">
-        <v>4.27</v>
+        <v>6.17</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1</v>
+        <v>0.63</v>
       </c>
       <c r="N47" t="n">
         <v>7.38</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.02</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>928</v>
+        <v>900</v>
       </c>
       <c r="I48" t="n">
         <v>902.3869283511472</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K48" t="n">
-        <v>3.48</v>
+        <v>0.36</v>
       </c>
       <c r="L48" t="n">
         <v>1.83</v>
@@ -3177,7 +3752,7 @@
         <v>0.41</v>
       </c>
       <c r="N48" t="n">
-        <v>2.15</v>
+        <v>4.39</v>
       </c>
       <c r="O48" t="n">
         <v>1.5</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.84</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>932.2</v>
+        <v>946.4</v>
       </c>
       <c r="I49" t="n">
         <v>939.4047299112079</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.58</v>
+        <v>-5.16</v>
       </c>
       <c r="L49" t="n">
         <v>6.38</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>7.59</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45617.55208333334</v>
+        <v>45618.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>907</v>
+        <v>886.4</v>
       </c>
       <c r="I50" t="n">
         <v>896.2477715673681</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.16</v>
+        <v>-6.34</v>
       </c>
       <c r="L50" t="n">
-        <v>5.94</v>
+        <v>6.59</v>
       </c>
       <c r="M50" t="n">
         <v>0.49</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>9.02</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45622.55208333334</v>
+        <v>45623.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>949</v>
+        <v>977.1</v>
       </c>
       <c r="I51" t="n">
         <v>953.4200775473736</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>-7.06</v>
+        <v>-10.23</v>
       </c>
       <c r="L51" t="n">
-        <v>7.89</v>
+        <v>12.79</v>
       </c>
       <c r="M51" t="n">
         <v>1.14</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>1008.5</v>
+        <v>990</v>
       </c>
       <c r="I52" t="n">
         <v>991.0530225063778</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>3.21</v>
+        <v>1.32</v>
       </c>
       <c r="L52" t="n">
         <v>3.27</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.39</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45728.55208333334</v>
+        <v>45729.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>665</v>
+        <v>684.8</v>
       </c>
       <c r="I53" t="n">
         <v>680.1739442276053</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>82</v>
+        <v>82.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>32.83</v>
+        <v>30.83</v>
       </c>
       <c r="L53" t="n">
         <v>6.83</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>9.1</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>740.6</v>
+        <v>691.2</v>
       </c>
       <c r="I54" t="n">
         <v>710.2346049391258</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K54" t="n">
-        <v>8.15</v>
+        <v>0.93</v>
       </c>
       <c r="L54" t="n">
         <v>3.97</v>
       </c>
       <c r="M54" t="n">
-        <v>0.84</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>3.66</v>
+        <v>4.19</v>
       </c>
       <c r="O54" t="n">
         <v>2.66</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>10.65</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>762.1</v>
+        <v>769</v>
       </c>
       <c r="I55" t="n">
         <v>764.8044863359418</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>-10.26</v>
+        <v>-11.26</v>
       </c>
       <c r="L55" t="n">
         <v>11.31</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>8.23</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45779.55208333334</v>
+        <v>45782.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>765.7</v>
+        <v>758.8</v>
       </c>
       <c r="I56" t="n">
         <v>764.5475934348747</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.43</v>
+        <v>-1.33</v>
       </c>
       <c r="L56" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="M56" t="n">
         <v>0.1</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>6.82</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45792.55208333334</v>
+        <v>45793.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>746</v>
+        <v>779.2</v>
       </c>
       <c r="I57" t="n">
         <v>749.6766429581492</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K57" t="n">
-        <v>1.69</v>
+        <v>-2.69</v>
       </c>
       <c r="L57" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="M57" t="n">
         <v>4.6</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>826.8</v>
+        <v>813.6</v>
       </c>
       <c r="I58" t="n">
         <v>818.7945814597754</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>6.11</v>
+        <v>4.41</v>
       </c>
       <c r="L58" t="n">
         <v>4.08</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.56</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45828.55208333334</v>
+        <v>45831.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>833.4</v>
+        <v>844</v>
       </c>
       <c r="I59" t="n">
         <v>843.0691273202035</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.43</v>
+        <v>-3.74</v>
       </c>
       <c r="L59" t="n">
         <v>4.4</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>7.73</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>836</v>
+        <v>815</v>
       </c>
       <c r="I60" t="n">
         <v>817.4193202641909</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.95</v>
+        <v>-3.44</v>
       </c>
       <c r="L60" t="n">
-        <v>3.07</v>
+        <v>4.62</v>
       </c>
       <c r="M60" t="n">
         <v>0.29</v>
       </c>
       <c r="N60" t="n">
-        <v>1.71</v>
+        <v>2.73</v>
       </c>
       <c r="O60" t="n">
         <v>0.9399999999999999</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>5.72</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>773.1</v>
+        <v>782.8</v>
       </c>
       <c r="I61" t="n">
         <v>776.7201156422987</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K61" t="n">
-        <v>5.14</v>
+        <v>3.95</v>
       </c>
       <c r="L61" t="n">
         <v>5.25</v>
       </c>
       <c r="M61" t="n">
-        <v>0.77</v>
+        <v>1.28</v>
       </c>
       <c r="N61" t="n">
         <v>3.61</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.93</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45895.38541666666</v>
+        <v>45895.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>754.2</v>
+        <v>745.7</v>
       </c>
       <c r="I62" t="n">
         <v>752.7835521140522</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.65</v>
+        <v>-4.74</v>
       </c>
       <c r="L62" t="n">
-        <v>4.31</v>
+        <v>4.93</v>
       </c>
       <c r="M62" t="n">
         <v>0.26</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>4.7</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45901.38541666666</v>
+        <v>45901.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>764.2</v>
+        <v>769.7</v>
       </c>
       <c r="I63" t="n">
         <v>764.361703830956</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.48</v>
+        <v>-3.22</v>
       </c>
       <c r="L63" t="n">
-        <v>2.53</v>
+        <v>3.26</v>
       </c>
       <c r="M63" t="n">
         <v>0.43</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.12</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>796</v>
+        <v>783.7</v>
       </c>
       <c r="I64" t="n">
         <v>791.4557779976603</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>3.42</v>
+        <v>1.82</v>
       </c>
       <c r="L64" t="n">
         <v>2.38</v>
@@ -4089,7 +4856,7 @@
         <v>0.12</v>
       </c>
       <c r="N64" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="O64" t="n">
         <v>3.82</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>4.88</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45954.55208333334</v>
+        <v>45957.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>776.4</v>
+        <v>791.7</v>
       </c>
       <c r="I65" t="n">
         <v>783.7424679022872</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K65" t="n">
-        <v>0.93</v>
+        <v>-1.02</v>
       </c>
       <c r="L65" t="n">
         <v>1.76</v>
@@ -4146,7 +4925,7 @@
         <v>0.79</v>
       </c>
       <c r="N65" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="O65" t="n">
         <v>-2.55</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>4.57</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45958.55208333334</v>
+        <v>45959.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>794</v>
+        <v>768.1</v>
       </c>
       <c r="I66" t="n">
         <v>770.304268882935</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>0.29</v>
+        <v>-2.98</v>
       </c>
       <c r="L66" t="n">
-        <v>1.93</v>
+        <v>6.08</v>
       </c>
       <c r="M66" t="n">
-        <v>0.06</v>
+        <v>2.14</v>
       </c>
       <c r="N66" t="n">
-        <v>-0</v>
+        <v>2.93</v>
       </c>
       <c r="O66" t="n">
         <v>2.27</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>4.14</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>766.9</v>
+        <v>793.3</v>
       </c>
       <c r="I67" t="n">
         <v>779.7049843529571</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K67" t="n">
-        <v>0.16</v>
+        <v>-3.28</v>
       </c>
       <c r="L67" t="n">
-        <v>3.63</v>
+        <v>4.67</v>
       </c>
       <c r="M67" t="n">
         <v>0.54</v>
       </c>
       <c r="N67" t="n">
-        <v>2.53</v>
+        <v>3.33</v>
       </c>
       <c r="O67" t="n">
         <v>-2.93</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>6.15</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45995.55208333334</v>
+        <v>45996.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>792.4</v>
+        <v>767.2</v>
       </c>
       <c r="I68" t="n">
         <v>768.1846729094018</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.11</v>
+        <v>-3.29</v>
       </c>
       <c r="L68" t="n">
-        <v>3.95</v>
+        <v>4.36</v>
       </c>
       <c r="M68" t="n">
         <v>0.74</v>
       </c>
       <c r="N68" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="O68" t="n">
         <v>3.33</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.57</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46056.55208333334</v>
+        <v>46057.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>726.6</v>
+        <v>735</v>
       </c>
       <c r="I69" t="n">
         <v>729.6572553690499</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K69" t="n">
-        <v>5.29</v>
+        <v>4.2</v>
       </c>
       <c r="L69" t="n">
         <v>3.62</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>8.85</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46076.55208333334</v>
+        <v>46077.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>718.5</v>
+        <v>706.8</v>
       </c>
       <c r="I70" t="n">
         <v>709.1937543161959</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.24</v>
+        <v>-3.84</v>
       </c>
       <c r="L70" t="n">
-        <v>3.4</v>
+        <v>4.29</v>
       </c>
       <c r="M70" t="n">
         <v>0.98</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>5.39</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46092.38541666666</v>
+        <v>46092.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>676.2</v>
+        <v>677.5</v>
       </c>
       <c r="I71" t="n">
         <v>676.6962088432872</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K71" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="L71" t="n">
         <v>1.7</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>6.51</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46094.55208333334</v>
+        <v>46097.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>644.95</v>
+        <v>626</v>
       </c>
       <c r="I72" t="n">
         <v>633.3996121013838</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K72" t="n">
-        <v>-4.8</v>
+        <v>-7.6</v>
       </c>
       <c r="L72" t="n">
-        <v>5.28</v>
+        <v>8.01</v>
       </c>
       <c r="M72" t="n">
         <v>1.11</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>8.76</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46114.55208333334</v>
+        <v>46118.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>660</v>
+        <v>669.25</v>
       </c>
       <c r="I73" t="n">
         <v>666.218901959568</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K73" t="n">
-        <v>-5.43</v>
+        <v>-6.91</v>
       </c>
       <c r="L73" t="n">
-        <v>6.92</v>
+        <v>7.35</v>
       </c>
       <c r="M73" t="n">
         <v>2.82</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>9.98</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46142.55208333334</v>
+        <v>46146.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>742</v>
+        <v>726.35</v>
       </c>
       <c r="I74" t="n">
         <v>727.3519717828856</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K74" t="n">
-        <v>10.87</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="L74" t="n">
         <v>3.38</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>8.08</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46146.55208333334</v>
+        <v>46147.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>733</v>
+        <v>787.55</v>
       </c>
       <c r="I75" t="n">
         <v>772.6461035873429</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.92</v>
+        <v>-8.43</v>
       </c>
       <c r="L75" t="n">
-        <v>3.34</v>
+        <v>10.05</v>
       </c>
       <c r="M75" t="n">
         <v>1.08</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="O75" t="n">
         <v>-1.21</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>10.41</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>786.2</v>
+        <v>771.85</v>
       </c>
       <c r="I76" t="n">
         <v>784.8265392833856</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.17</v>
+        <v>-1.99</v>
       </c>
       <c r="L76" t="n">
         <v>6.29</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>6.42</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>759.5</v>
+        <v>781</v>
       </c>
       <c r="I77" t="n">
         <v>764.8301679536838</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K77" t="n">
-        <v>1.6</v>
+        <v>-1.19</v>
       </c>
       <c r="L77" t="n">
         <v>4.61</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>6.73</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46209.55208333334</v>
+        <v>46210.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>788.5</v>
+        <v>773.8</v>
       </c>
       <c r="I78" t="n">
         <v>779.014754745036</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K78" t="n">
-        <v>0.96</v>
+        <v>-0.92</v>
       </c>
       <c r="L78" t="n">
         <v>1.66</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>5.93</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46231.38541666666</v>
+        <v>46231.55208333334</v>
       </c>
       <c r="H79" t="n">
-        <v>784.5</v>
+        <v>802.7</v>
       </c>
       <c r="I79" t="n">
         <v>786.8380258072052</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K79" t="n">
-        <v>-1.38</v>
+        <v>-3.73</v>
       </c>
       <c r="L79" t="n">
-        <v>2.79</v>
+        <v>3.9</v>
       </c>
       <c r="M79" t="n">
         <v>0.55</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>6.09</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46247.55208333334</v>
+        <v>46248.38541666666</v>
       </c>
       <c r="H80" t="n">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="I80" t="n">
         <v>768.2146756321793</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K80" t="n">
-        <v>-3.82</v>
+        <v>-4.82</v>
       </c>
       <c r="L80" t="n">
-        <v>4.24</v>
+        <v>5.13</v>
       </c>
       <c r="M80" t="n">
         <v>0.64</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5037,28 +6008,28 @@
         <v>5.39</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46262.55208333334</v>
+        <v>46265.38541666666</v>
       </c>
       <c r="H81" t="n">
-        <v>760</v>
+        <v>776.25</v>
       </c>
       <c r="I81" t="n">
         <v>768.5822761281822</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.52</v>
+        <v>-1.6</v>
       </c>
       <c r="L81" t="n">
-        <v>1.57</v>
+        <v>2.68</v>
       </c>
       <c r="M81" t="n">
         <v>1.05</v>
       </c>
       <c r="N81" t="n">
-        <v>2.58</v>
+        <v>3.28</v>
       </c>
       <c r="O81" t="n">
         <v>-1.3</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,22 +6077,22 @@
         <v>6.02</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H82" t="n">
-        <v>752.9</v>
+        <v>736.5</v>
       </c>
       <c r="I82" t="n">
         <v>744.2746936322997</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>-3.01</v>
+        <v>-5.12</v>
       </c>
       <c r="L82" t="n">
-        <v>3.38</v>
+        <v>5.89</v>
       </c>
       <c r="M82" t="n">
         <v>0.25</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S82" t="b">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>6.52</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H83" t="n">
-        <v>693.4</v>
+        <v>706.15</v>
       </c>
       <c r="I83" t="n">
         <v>703.3583119320675</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K83" t="n">
-        <v>5.85</v>
+        <v>4.12</v>
       </c>
       <c r="L83" t="n">
         <v>2.89</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>5.65</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46317.38541666666</v>
+        <v>46317.55208333334</v>
       </c>
       <c r="H84" t="n">
-        <v>672.35</v>
+        <v>669</v>
       </c>
       <c r="I84" t="n">
         <v>670.8619783791175</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K84" t="n">
-        <v>-4.79</v>
+        <v>-5.26</v>
       </c>
       <c r="L84" t="n">
         <v>5.98</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5289,6 +6308,12 @@
       <c r="Q85" t="n">
         <v>7</v>
       </c>
+      <c r="R85" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7391,7 +8416,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -7401,7 +8426,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -7411,7 +8436,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="8">
@@ -7421,7 +8446,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7431,7 +8456,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -7441,7 +8466,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35.2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -7481,7 +8506,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.15</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="15">
@@ -7491,7 +8516,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="16">
@@ -7501,7 +8526,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="17">
@@ -7511,7 +8536,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.83</v>
+        <v>30.83</v>
       </c>
     </row>
     <row r="18">
@@ -7521,7 +8546,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="19">
@@ -7531,7 +8556,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.91</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="20">
@@ -7541,7 +8566,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.38</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="21">
@@ -7551,7 +8576,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.5</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="22">
@@ -7561,7 +8586,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -7571,7 +8596,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -7581,7 +8606,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="25">
@@ -7591,7 +8616,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.91</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -7601,7 +8626,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.12</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="27">
@@ -7611,7 +8636,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.38</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="28">
@@ -7621,7 +8646,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
